--- a/Start-Startup-Financial-Model/Start-Startup-Financial-Model.xlsx
+++ b/Start-Startup-Financial-Model/Start-Startup-Financial-Model.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Documents\GitHub\Financial-Analysis-Portfolio\Start-Startup-Financial-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE8F5F3-7C63-4F23-AC6C-E8CFAEEC4168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E69DFC5-9A05-44C6-BA70-247C8A315DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51C94CC5-0C2F-6D4D-9C41-E0029B3FD163}"/>
   </bookViews>
   <sheets>
-    <sheet name="Financial Model" sheetId="1" r:id="rId1"/>
+    <sheet name="Cover" sheetId="2" r:id="rId1"/>
+    <sheet name="Financial Model" sheetId="1" r:id="rId2"/>
+    <sheet name="__tracelight_scratchpad__" sheetId="3" state="veryHidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
   <si>
     <t>Income Statement</t>
   </si>
@@ -223,13 +225,88 @@
   </si>
   <si>
     <t>Average Order Value</t>
+  </si>
+  <si>
+    <t>STARTUP FINANCIAL MODEL</t>
+  </si>
+  <si>
+    <t>12-MONTH FORECAST | EXECUTIVE CONTROL CENTER</t>
+  </si>
+  <si>
+    <t>Executive Overview</t>
+  </si>
+  <si>
+    <t>A decision-ready view of operating assumptions, revenue build, cost structure, and profitability.</t>
+  </si>
+  <si>
+    <t>MODEL PROFILE</t>
+  </si>
+  <si>
+    <t>Forecast period</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>Model type</t>
+  </si>
+  <si>
+    <t>Primary use</t>
+  </si>
+  <si>
+    <t>KEY METRICS</t>
+  </si>
+  <si>
+    <t>Annual revenue</t>
+  </si>
+  <si>
+    <t>Month 1 profit / (loss)</t>
+  </si>
+  <si>
+    <t>Month 12 profit / (loss)</t>
+  </si>
+  <si>
+    <t>Break-even month</t>
+  </si>
+  <si>
+    <t>Ending gross margin</t>
+  </si>
+  <si>
+    <t>Month 12 total costs</t>
+  </si>
+  <si>
+    <t>KEY TAKEAWAYS</t>
+  </si>
+  <si>
+    <t>WORKBOOK NAVIGATION</t>
+  </si>
+  <si>
+    <t>MANAGEMENT READOUT</t>
+  </si>
+  <si>
+    <t>Use the linked model sections to flex drivers and review monthly outcomes.</t>
+  </si>
+  <si>
+    <t>Driver-based forecast</t>
+  </si>
+  <si>
+    <t>Revenue, cost, and break-even analysis</t>
+  </si>
+  <si>
+    <t>Mohamed Magdy | FP&amp;A Analyst | MBA Candidate</t>
+  </si>
+  <si>
+    <t>Tanta, Al-Gharbia, Egypt | +20 101 301 9563 | mohamedeones123@gmail.com</t>
+  </si>
+  <si>
+    <t>PROFESSIONAL LINKS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -237,8 +314,10 @@
     <numFmt numFmtId="167" formatCode="[$$-409]#,##0.00;[Red][$$-409]#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="#,##0;\(#,##0\);&quot;--&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0%;\(0.0%\);&quot;--&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -326,8 +405,96 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,8 +531,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F3F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -402,13 +593,204 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E78"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1F4E78"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E78"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E78"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E78"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1F4E78"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1F4E78"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1F4E78"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7C9E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C9E2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7C9E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7C9E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7C9E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C9E2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7C9E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C9E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -486,6 +868,299 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="15" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2905,7 +3580,538 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{38772BB1-A5FD-43D9-9794-97E0D019CEF0}">
+  <we:reference id="wa200008399" version="1.0.0.5" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200008399" version="1.0.0.5" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="ProjectMetadata" value="&quot;{\&quot;projectId\&quot;:\&quot;2c5126c1-ba01-4e92-9c50-84e4755c9fa3\&quot;}&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B14C036-AE33-4CCD-A4E6-1144C39A6D75}">
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="7" width="14" customWidth="1"/>
+    <col min="8" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="29" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="16" width="13" customWidth="1"/>
+    <col min="17" max="16384" width="9" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46"/>
+      <c r="B1" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+    </row>
+    <row r="2" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="123" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="123"/>
+    </row>
+    <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="125" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="126"/>
+      <c r="J3" s="128" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="129"/>
+    </row>
+    <row r="4" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+    </row>
+    <row r="5" spans="1:16" ht="33.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="118" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="119"/>
+      <c r="P5" s="120"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="J7" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55">
+        <f>'Financial Model'!D3</f>
+        <v>46023</v>
+      </c>
+      <c r="E8" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="55">
+        <f>'Financial Model'!O3</f>
+        <v>46357</v>
+      </c>
+      <c r="G8" s="61"/>
+      <c r="J8" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="69">
+        <f>SUM('Financial Model'!D37:O37)</f>
+        <v>88341.950445960945</v>
+      </c>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="75"/>
+    </row>
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="53"/>
+      <c r="D9" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="106"/>
+      <c r="J9" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="64"/>
+      <c r="L9" s="65">
+        <f>'Financial Model'!D58</f>
+        <v>-1800.4</v>
+      </c>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="76"/>
+    </row>
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="107" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="108"/>
+      <c r="J10" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="64"/>
+      <c r="L10" s="65">
+        <f>'Financial Model'!O58</f>
+        <v>5284.0314356744511</v>
+      </c>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="76"/>
+    </row>
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="64"/>
+      <c r="L11" s="66">
+        <f>IFERROR(INDEX(B28:M28,1,MATCH(1,B27:M27,0)),"Not reached")</f>
+        <v>46204</v>
+      </c>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="76"/>
+    </row>
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="64"/>
+      <c r="L12" s="67">
+        <f>'Financial Model'!O40</f>
+        <v>0.75514746800222587</v>
+      </c>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="76"/>
+    </row>
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71">
+        <f>'Financial Model'!O54</f>
+        <v>9315.0616092187483</v>
+      </c>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="77"/>
+    </row>
+    <row r="14" spans="1:16" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="J15" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+    </row>
+    <row r="16" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="131" t="str">
+        <f>"Revenue grows from "&amp;TEXT('Financial Model'!D37,"$#,##0")&amp;" in "&amp;TEXT('Financial Model'!D3,"mmm-yy")&amp;" to "&amp;TEXT('Financial Model'!O37,"$#,##0")&amp;" by "&amp;TEXT('Financial Model'!O3,"mmm-yy")&amp;"."</f>
+        <v>Revenue grows from $1,000 in Jan-26 to $16,004 by Dec-26.</v>
+      </c>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="133"/>
+      <c r="J16" s="109" t="str">
+        <f>HYPERLINK("#'Financial Model'!B4","01  ASSUMPTIONS")</f>
+        <v>01  ASSUMPTIONS</v>
+      </c>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="111"/>
+    </row>
+    <row r="17" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="134" t="str">
+        <f>"Gross margin expands from "&amp;TEXT('Financial Model'!D40,"0.0%")&amp;" to "&amp;TEXT('Financial Model'!O40,"0.0%")&amp;"."</f>
+        <v>Gross margin expands from 50.0% to 75.5%.</v>
+      </c>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="136"/>
+      <c r="J17" s="112" t="str">
+        <f>HYPERLINK("#'Financial Model'!B36","02  INCOME STATEMENT")</f>
+        <v>02  INCOME STATEMENT</v>
+      </c>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="113"/>
+      <c r="P17" s="114"/>
+    </row>
+    <row r="18" spans="2:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="134" t="str">
+        <f>"Positive profit begins in "&amp;TEXT($L$11,"mmm-yy")&amp;", based on the current operating assumptions."</f>
+        <v>Positive profit begins in Jul-26, based on the current operating assumptions.</v>
+      </c>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
+      <c r="J18" s="115" t="str">
+        <f>HYPERLINK("#'Financial Model'!A61","03  CHARTS &amp; VISUALS")</f>
+        <v>03  CHARTS &amp; VISUALS</v>
+      </c>
+      <c r="K18" s="116"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="116"/>
+      <c r="N18" s="116"/>
+      <c r="O18" s="116"/>
+      <c r="P18" s="117"/>
+    </row>
+    <row r="19" spans="2:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="137" t="str">
+        <f>"Total costs reach "&amp;TEXT('Financial Model'!O54,"$#,##0")&amp;" in "&amp;TEXT('Financial Model'!O3,"mmm-yy")&amp;"."</f>
+        <v>Total costs reach $9,315 in Dec-26.</v>
+      </c>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="139"/>
+    </row>
+    <row r="20" spans="2:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J20" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+    </row>
+    <row r="21" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="98" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="100"/>
+    </row>
+    <row r="22" spans="2:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="99"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="101"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="140" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="141"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="130" t="str">
+        <f>HYPERLINK("https://www.linkedin.com/in/mohamed-magdy-finance","LinkedIn")</f>
+        <v>LinkedIn</v>
+      </c>
+      <c r="K24" s="121"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="130" t="str">
+        <f>HYPERLINK("https://github.com/Mohamed-Magdy-Finance","GitHub")</f>
+        <v>GitHub</v>
+      </c>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="122"/>
+    </row>
+    <row r="27" spans="2:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="45">
+        <f>IF('Financial Model'!D58&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="45">
+        <f>IF('Financial Model'!E58&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="45">
+        <f>IF('Financial Model'!F58&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="45">
+        <f>IF('Financial Model'!G58&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="45">
+        <f>IF('Financial Model'!H58&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="45">
+        <f>IF('Financial Model'!I58&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="45">
+        <f>IF('Financial Model'!J58&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="45">
+        <f>IF('Financial Model'!K58&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="45">
+        <f>IF('Financial Model'!L58&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K27" s="45">
+        <f>IF('Financial Model'!M58&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L27" s="45">
+        <f>IF('Financial Model'!N58&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M27" s="45">
+        <f>IF('Financial Model'!O58&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="44">
+        <f>'Financial Model'!D3</f>
+        <v>46023</v>
+      </c>
+      <c r="C28" s="44">
+        <f>'Financial Model'!E3</f>
+        <v>46054</v>
+      </c>
+      <c r="D28" s="44">
+        <f>'Financial Model'!F3</f>
+        <v>46082</v>
+      </c>
+      <c r="E28" s="44">
+        <f>'Financial Model'!G3</f>
+        <v>46113</v>
+      </c>
+      <c r="F28" s="44">
+        <f>'Financial Model'!H3</f>
+        <v>46143</v>
+      </c>
+      <c r="G28" s="44">
+        <f>'Financial Model'!I3</f>
+        <v>46174</v>
+      </c>
+      <c r="H28" s="44">
+        <f>'Financial Model'!J3</f>
+        <v>46204</v>
+      </c>
+      <c r="I28" s="44">
+        <f>'Financial Model'!K3</f>
+        <v>46235</v>
+      </c>
+      <c r="J28" s="44">
+        <f>'Financial Model'!L3</f>
+        <v>46266</v>
+      </c>
+      <c r="K28" s="44">
+        <f>'Financial Model'!M3</f>
+        <v>46296</v>
+      </c>
+      <c r="L28" s="44">
+        <f>'Financial Model'!N3</f>
+        <v>46327</v>
+      </c>
+      <c r="M28" s="44">
+        <f>'Financial Model'!O3</f>
+        <v>46357</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" scale="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BAF0A7-6C3E-5B41-B94B-78E46A3C64F1}">
   <dimension ref="A2:O76"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5083,4 +6289,130 @@
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3554C32-02B7-4645-AEEF-94C31BD0BE58}">
+  <dimension ref="A41:O63"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="62"/>
+    </row>
+    <row r="42" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="63"/>
+    </row>
+    <row r="43" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="90"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="93"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="91"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="87"/>
+      <c r="D45" s="87"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="94"/>
+    </row>
+    <row r="46" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="92"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="89"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="95"/>
+    </row>
+    <row r="47" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="51"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="50"/>
+      <c r="L48" s="50"/>
+      <c r="M48" s="50"/>
+      <c r="N48" s="50"/>
+      <c r="O48" s="52"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="103"/>
+      <c r="B54" s="102"/>
+      <c r="C54" s="102"/>
+      <c r="D54" s="102"/>
+      <c r="E54" s="102"/>
+      <c r="F54" s="102"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="102"/>
+      <c r="B56" s="102"/>
+      <c r="C56" s="102"/>
+      <c r="D56" s="102"/>
+      <c r="E56" s="102"/>
+      <c r="F56" s="102"/>
+      <c r="G56" s="104"/>
+    </row>
+    <row r="57" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="81"/>
+      <c r="B58" s="79"/>
+      <c r="C58" s="79"/>
+      <c r="D58" s="79"/>
+      <c r="E58" s="79"/>
+      <c r="F58" s="84"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="82"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="78"/>
+      <c r="F59" s="85"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="82"/>
+      <c r="B60" s="78"/>
+      <c r="C60" s="78"/>
+      <c r="D60" s="78"/>
+      <c r="E60" s="78"/>
+      <c r="F60" s="85"/>
+    </row>
+    <row r="61" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="83"/>
+      <c r="B61" s="80"/>
+      <c r="C61" s="80"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="80"/>
+      <c r="F61" s="86"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="103"/>
+      <c r="B63" s="102"/>
+      <c r="C63" s="102"/>
+      <c r="D63" s="102"/>
+      <c r="E63" s="102"/>
+      <c r="F63" s="104"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>